--- a/domrf.xlsx
+++ b/domrf.xlsx
@@ -2,23 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr codeName="ЭтаКнига" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shidlovskiyaf\projects\domrfparse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB3291E6-3E17-45B6-A42C-A8330F52394F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09D93AC2-345A-4A6C-A973-2E34A9AE901F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{8B0F0897-0962-2640-84B5-E0DB047216C8}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8B0F0897-0962-2640-84B5-E0DB047216C8}"/>
   </bookViews>
   <sheets>
-    <sheet name="sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Лист1" sheetId="2" r:id="rId1"/>
+    <sheet name="sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sheet1!$B$1:$B$648</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">sheet1!$B$1:$B$682</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$A$36</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,60 +42,51 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="15">
   <si>
     <t>ID</t>
   </si>
   <si>
-    <t>70300</t>
-  </si>
-  <si>
-    <t>70309</t>
-  </si>
-  <si>
-    <t>70310</t>
-  </si>
-  <si>
-    <t>70368</t>
-  </si>
-  <si>
-    <t>70374</t>
-  </si>
-  <si>
-    <t>70416</t>
-  </si>
-  <si>
-    <t>70442</t>
-  </si>
-  <si>
-    <t>70547</t>
-  </si>
-  <si>
-    <t>70548</t>
-  </si>
-  <si>
-    <t>70585</t>
-  </si>
-  <si>
-    <t>70590</t>
-  </si>
-  <si>
-    <t>70610</t>
-  </si>
-  <si>
-    <t>70663</t>
-  </si>
-  <si>
-    <t>70684</t>
-  </si>
-  <si>
-    <t>70718</t>
-  </si>
-  <si>
-    <t>70778</t>
-  </si>
-  <si>
-    <t>70783</t>
+    <t>Преображенская площадь</t>
+  </si>
+  <si>
+    <t>Инноватор</t>
+  </si>
+  <si>
+    <t>Инсайдер / Insider</t>
+  </si>
+  <si>
+    <t>Дом XXII</t>
+  </si>
+  <si>
+    <t>Вейв / Wave</t>
+  </si>
+  <si>
+    <t>Эвопарк Измайлово / EvoPark Измайлово</t>
+  </si>
+  <si>
+    <t>Phantom</t>
+  </si>
+  <si>
+    <t>Назаре / Мангазея в Богородском</t>
+  </si>
+  <si>
+    <t>Солос / Solos</t>
+  </si>
+  <si>
+    <t>Узоры</t>
+  </si>
+  <si>
+    <t>Гранд Фили</t>
+  </si>
+  <si>
+    <t>Русские Сезоны</t>
+  </si>
+  <si>
+    <t>Лучи</t>
+  </si>
+  <si>
+    <t>Энигмия</t>
   </si>
 </sst>
 </file>
@@ -130,8 +123,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -445,102 +439,359 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{430466FA-FD0A-465C-9E42-4840CA44E247}">
+  <sheetPr codeName="Лист1"/>
+  <dimension ref="A1:A27"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="58.69921875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F73AF8DC-B155-A248-9B56-2C3EBABC4DDA}">
-  <dimension ref="B1:B18"/>
+  <sheetPr codeName="Лист2"/>
+  <dimension ref="B1:D51"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B18" t="s">
-        <v>17</v>
-      </c>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B2">
+        <v>59887</v>
+      </c>
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B3">
+        <v>63450</v>
+      </c>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>44742</v>
+      </c>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>41967</v>
+      </c>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>41962</v>
+      </c>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>46019</v>
+      </c>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>46020</v>
+      </c>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>46021</v>
+      </c>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>47784</v>
+      </c>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>61521</v>
+      </c>
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>63603</v>
+      </c>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>36266</v>
+      </c>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>47544</v>
+      </c>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>47545</v>
+      </c>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D19" s="1"/>
+    </row>
+    <row r="20" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D20" s="1"/>
+    </row>
+    <row r="21" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D21" s="1"/>
+    </row>
+    <row r="22" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D22" s="1"/>
+    </row>
+    <row r="23" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D23" s="1"/>
+    </row>
+    <row r="24" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D24" s="1"/>
+    </row>
+    <row r="25" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D25" s="1"/>
+    </row>
+    <row r="26" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D26" s="1"/>
+    </row>
+    <row r="27" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D27" s="1"/>
+    </row>
+    <row r="28" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D28" s="1"/>
+    </row>
+    <row r="29" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D29" s="1"/>
+    </row>
+    <row r="30" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D30" s="1"/>
+    </row>
+    <row r="31" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D31" s="1"/>
+    </row>
+    <row r="32" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D32" s="1"/>
+    </row>
+    <row r="33" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D33" s="1"/>
+    </row>
+    <row r="34" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D34" s="1"/>
+    </row>
+    <row r="35" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D35" s="1"/>
+    </row>
+    <row r="36" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D36" s="1"/>
+    </row>
+    <row r="37" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D37" s="1"/>
+    </row>
+    <row r="38" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D38" s="1"/>
+    </row>
+    <row r="39" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D39" s="1"/>
+    </row>
+    <row r="40" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D40" s="1"/>
+    </row>
+    <row r="41" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D41" s="1"/>
+    </row>
+    <row r="42" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D42" s="1"/>
+    </row>
+    <row r="43" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D43" s="1"/>
+    </row>
+    <row r="44" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D44" s="1"/>
+    </row>
+    <row r="45" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D45" s="1"/>
+    </row>
+    <row r="46" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D46" s="1"/>
+    </row>
+    <row r="47" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D47" s="1"/>
+    </row>
+    <row r="48" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D48" s="1"/>
+    </row>
+    <row r="49" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D49" s="1"/>
+    </row>
+    <row r="50" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D50" s="1"/>
+    </row>
+    <row r="51" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D51" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="B1:B648" xr:uid="{F73AF8DC-B155-A248-9B56-2C3EBABC4DDA}"/>
+  <autoFilter ref="B1:B682" xr:uid="{F73AF8DC-B155-A248-9B56-2C3EBABC4DDA}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>